--- a/data/trans_dic/DC_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,62</t>
+          <t>3,88; 13,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 31,38</t>
+          <t>18,71; 31,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,3; 19,52</t>
+          <t>11,6; 19,56</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 15,34</t>
+          <t>7,75; 15,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,13; 61,1</t>
+          <t>25,8; 62,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,92; 43,41</t>
+          <t>18,17; 43,76</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,2; 20,19</t>
+          <t>12,89; 19,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,07; 33,16</t>
+          <t>21,34; 32,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 25,36</t>
+          <t>19,35; 25,15</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 26,6</t>
+          <t>8,05; 26,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,79; 40,17</t>
+          <t>31,64; 40,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,38; 32,27</t>
+          <t>16,81; 32,56</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,95; 34,55</t>
+          <t>27,47; 34,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,74; 49,06</t>
+          <t>43,0; 49,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,8; 40,85</t>
+          <t>35,86; 40,85</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,4; 36,15</t>
+          <t>28,31; 36,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49,54; 85,91</t>
+          <t>49,4; 85,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,18; 75,06</t>
+          <t>41,22; 75,69</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,95; 49,86</t>
+          <t>40,54; 49,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60,88; 67,8</t>
+          <t>61,12; 67,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,84; 59,31</t>
+          <t>53,88; 59,23</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,15; 23,88</t>
+          <t>16,48; 23,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39,58; 54,24</t>
+          <t>39,55; 54,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,83; 40,09</t>
+          <t>30,08; 39,43</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15927; 58463</t>
+          <t>15509; 55506</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58459; 98273</t>
+          <t>58612; 97501</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80562; 139182</t>
+          <t>82763; 139522</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32133; 64971</t>
+          <t>32806; 64169</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128688; 312893</t>
+          <t>132129; 322204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167676; 406140</t>
+          <t>170030; 409408</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70803; 108291</t>
+          <t>69134; 106263</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>130681; 196303</t>
+          <t>126323; 194608</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>216069; 286190</t>
+          <t>218364; 283737</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68771; 236125</t>
+          <t>71450; 238114</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>219461; 286364</t>
+          <t>225560; 288326</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>246106; 516591</t>
+          <t>269069; 521243</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>151253; 193898</t>
+          <t>154190; 195312</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>234158; 268790</t>
+          <t>235573; 269643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>397035; 453118</t>
+          <t>397704; 453083</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>104547; 133080</t>
+          <t>104231; 133128</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>301386; 522675</t>
+          <t>300536; 518053</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>402129; 732950</t>
+          <t>402547; 739175</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>115801; 140976</t>
+          <t>114641; 140247</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>259237; 288732</t>
+          <t>260250; 287859</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>381476; 420286</t>
+          <t>381785; 419730</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>593275; 826212</t>
+          <t>570239; 823821</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1469461; 2013722</t>
+          <t>1468343; 2005111</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2139444; 2875621</t>
+          <t>2157419; 2827859</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,88</t>
+          <t>4,4; 13,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,71; 31,13</t>
+          <t>18,81; 32,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 19,56</t>
+          <t>12,6; 21,01</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 15,15</t>
+          <t>7,75; 14,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,8; 62,92</t>
+          <t>21,84; 30,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,17; 43,76</t>
+          <t>15,64; 21,24</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,89; 19,81</t>
+          <t>12,49; 18,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,34; 32,87</t>
+          <t>28,61; 35,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,35; 25,15</t>
+          <t>21,59; 25,94</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 26,82</t>
+          <t>21,55; 28,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,64; 40,45</t>
+          <t>36,1; 41,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,81; 32,56</t>
+          <t>29,92; 34,35</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,26%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,47; 34,8</t>
+          <t>26,96; 34,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,0; 49,21</t>
+          <t>43,34; 49,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,86; 40,85</t>
+          <t>35,83; 40,68</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,31; 36,16</t>
+          <t>27,92; 35,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49,4; 85,15</t>
+          <t>48,46; 55,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,22; 75,69</t>
+          <t>39,54; 44,9</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,08%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,54; 49,6</t>
+          <t>40,63; 49,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61,12; 67,6</t>
+          <t>61,55; 67,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,88; 59,23</t>
+          <t>54,25; 59,72</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,48; 23,81</t>
+          <t>21,51; 24,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39,55; 54,01</t>
+          <t>39,19; 41,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,08; 39,43</t>
+          <t>30,88; 33,05</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>33334</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76671</t>
+          <t>90990</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107961</t>
+          <t>124324</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15509; 55506</t>
+          <t>17931; 56970</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58612; 97501</t>
+          <t>68193; 116661</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82763; 139522</t>
+          <t>97055; 161863</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>45953</t>
+          <t>51592</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>188168</t>
+          <t>129334</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234121</t>
+          <t>180925</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32806; 64169</t>
+          <t>36938; 71010</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>132129; 322204</t>
+          <t>109569; 150610</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170030; 409408</t>
+          <t>153091; 207879</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86562</t>
+          <t>95548</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>170884</t>
+          <t>198565</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257446</t>
+          <t>294113</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>69134; 106263</t>
+          <t>77569; 115383</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>126323; 194608</t>
+          <t>178297; 218948</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>218364; 283737</t>
+          <t>268629; 322748</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>163566</t>
+          <t>174398</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>261928</t>
+          <t>286077</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>425494</t>
+          <t>460476</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71450; 238114</t>
+          <t>150997; 200176</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>225560; 288326</t>
+          <t>266027; 308436</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>269069; 521243</t>
+          <t>430058; 493746</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>173923</t>
+          <t>184335</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>252420</t>
+          <t>281751</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>426343</t>
+          <t>466087</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>154190; 195312</t>
+          <t>164262; 207191</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>235573; 269643</t>
+          <t>263869; 300951</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>397704; 453083</t>
+          <t>436521; 495561</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>118499</t>
+          <t>129407</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>409189</t>
+          <t>227018</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>527688</t>
+          <t>356425</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>104231; 133128</t>
+          <t>113672; 146085</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>300536; 518053</t>
+          <t>212818; 242717</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>402547; 739175</t>
+          <t>334623; 379956</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>127804</t>
+          <t>140620</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>274490</t>
+          <t>301626</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>402294</t>
+          <t>442247</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>114641; 140247</t>
+          <t>126042; 154596</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>260250; 287859</t>
+          <t>285967; 315660</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>381785; 419730</t>
+          <t>420346; 462714</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>747597</t>
+          <t>809235</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1633750</t>
+          <t>1515362</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2381347</t>
+          <t>2324597</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>570239; 823821</t>
+          <t>759866; 864592</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1468343; 2005111</t>
+          <t>1464653; 1567010</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2157419; 2827859</t>
+          <t>2244812; 2402482</t>
         </is>
       </c>
     </row>
